--- a/survey_templates/049_property_maintenance_feedback_form--survey_templates.xlsx
+++ b/survey_templates/049_property_maintenance_feedback_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,7 +665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -715,29 +715,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>maintenance_request</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Maintenance Request</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>property_maintenance_feedback_form_2_choices</t>
+          <t>property_maintenance_feedback_form_3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>bugs_and_pests</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Bugs and Pests</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bugs_and_pests</t>
+          <t>leak_and_water_issues</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bugs and Pests</t>
+          <t>Leak and Water Issues</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>leak_and_water_issues</t>
+          <t>smell_odor_issues</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Leak and Water Issues</t>
+          <t>Smell Odor Issues</t>
         </is>
       </c>
     </row>
@@ -783,29 +783,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>smell_odor_issues</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Smell Odor Issues</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>property_maintenance_feedback_form_3_choices</t>
+          <t>property_maintenance_feedback_form_4_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Phone Call</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>phone_call</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phone Call</t>
+          <t>Text Message</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>text_message</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Text Message</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -851,27 +851,10 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>in-app_messaging</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>property_maintenance_feedback_form_4_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>in-app_messaging</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
         <is>
           <t>In-app Messaging</t>
         </is>
